--- a/Daily_Report/Top 7 broker List with its Turnover 2023-11-29.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2023-11-29.xlsx
@@ -98,67 +98,67 @@
     <t>42</t>
   </si>
   <si>
-    <t>123,373,254.3</t>
-  </si>
-  <si>
-    <t>121,114,737.32</t>
-  </si>
-  <si>
-    <t>104,751,216.7</t>
-  </si>
-  <si>
-    <t>95,583,645.1</t>
-  </si>
-  <si>
-    <t>83,816,175.69</t>
-  </si>
-  <si>
-    <t>81,873,248.05</t>
-  </si>
-  <si>
-    <t>74,882,437.59</t>
-  </si>
-  <si>
-    <t>106,679,204.8</t>
-  </si>
-  <si>
-    <t>54,395,915.2</t>
-  </si>
-  <si>
-    <t>10,442,880.3</t>
-  </si>
-  <si>
-    <t>22,305,794.8</t>
-  </si>
-  <si>
-    <t>44,151,535.4</t>
-  </si>
-  <si>
-    <t>50,619,005.5</t>
-  </si>
-  <si>
-    <t>35,163,012.46</t>
-  </si>
-  <si>
-    <t>16,694,049.5</t>
-  </si>
-  <si>
-    <t>66,718,822.12</t>
-  </si>
-  <si>
-    <t>94,308,336.4</t>
-  </si>
-  <si>
-    <t>73,277,850.3</t>
-  </si>
-  <si>
-    <t>39,664,640.29</t>
-  </si>
-  <si>
-    <t>31,254,242.55</t>
-  </si>
-  <si>
-    <t>39,719,425.13</t>
+    <t>123,991,793.3</t>
+  </si>
+  <si>
+    <t>122,672,503.22</t>
+  </si>
+  <si>
+    <t>105,423,940.9</t>
+  </si>
+  <si>
+    <t>96,261,673.9</t>
+  </si>
+  <si>
+    <t>84,584,766.3</t>
+  </si>
+  <si>
+    <t>82,811,296.84</t>
+  </si>
+  <si>
+    <t>75,395,896.19</t>
+  </si>
+  <si>
+    <t>107,064,764.8</t>
+  </si>
+  <si>
+    <t>55,434,620.6</t>
+  </si>
+  <si>
+    <t>10,748,006.9</t>
+  </si>
+  <si>
+    <t>22,880,669.6</t>
+  </si>
+  <si>
+    <t>44,638,104.0</t>
+  </si>
+  <si>
+    <t>51,190,011.5</t>
+  </si>
+  <si>
+    <t>35,293,697.46</t>
+  </si>
+  <si>
+    <t>16,927,028.5</t>
+  </si>
+  <si>
+    <t>67,237,882.62</t>
+  </si>
+  <si>
+    <t>94,675,934.0</t>
+  </si>
+  <si>
+    <t>73,381,004.3</t>
+  </si>
+  <si>
+    <t>39,946,662.29</t>
+  </si>
+  <si>
+    <t>31,621,285.35</t>
+  </si>
+  <si>
+    <t>40,102,198.72</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -218,13 +218,13 @@
     <t>5,237,058.2</t>
   </si>
   <si>
-    <t>4,639,100.5</t>
+    <t>4,815,770.5</t>
   </si>
   <si>
     <t>TRH</t>
   </si>
   <si>
-    <t>4,386,970.0</t>
+    <t>4,602,160.0</t>
   </si>
   <si>
     <t>PHCL</t>
@@ -296,13 +296,13 @@
     <t>SHL</t>
   </si>
   <si>
-    <t>4,635,078.4</t>
+    <t>4,795,750.09</t>
   </si>
   <si>
     <t>GCIL</t>
   </si>
   <si>
-    <t>1,812,689.5</t>
+    <t>1,817,114.5</t>
   </si>
   <si>
     <t>1,810,400.0</t>
@@ -317,7 +317,7 @@
     <t>8,215,382.0</t>
   </si>
   <si>
-    <t>4,565,008.5</t>
+    <t>4,870,308.5</t>
   </si>
   <si>
     <t>2,610,782.29</t>
@@ -365,7 +365,7 @@
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>1,490,881.0</t>
+    <t>1,503,085.0</t>
   </si>
   <si>
     <t>SHPC</t>
@@ -383,7 +383,7 @@
     <t>892,006.9</t>
   </si>
   <si>
-    <t>789,655.6</t>
+    <t>890,465.6</t>
   </si>
   <si>
     <t>9,872,124.6</t>
@@ -398,10 +398,10 @@
     <t>3,122,525.7</t>
   </si>
   <si>
-    <t>2,439,388.0</t>
-  </si>
-  <si>
-    <t>3,315,207.0</t>
+    <t>2,543,910.0</t>
+  </si>
+  <si>
+    <t>3,319,730.0</t>
   </si>
   <si>
     <t>HLI</t>
@@ -410,15 +410,15 @@
     <t>2,050,051.8</t>
   </si>
   <si>
+    <t>1,310,368.0</t>
+  </si>
+  <si>
     <t>HATHY</t>
   </si>
   <si>
     <t>1,204,005.0</t>
   </si>
   <si>
-    <t>1,162,468.0</t>
-  </si>
-  <si>
     <t>NICAD8182</t>
   </si>
   <si>
@@ -443,7 +443,7 @@
     <t>2,924,014.1</t>
   </si>
   <si>
-    <t>2,186,950.79</t>
+    <t>2,191,480.79</t>
   </si>
   <si>
     <t>1,930,282.0</t>
@@ -458,13 +458,13 @@
     <t>2,137,605.0</t>
   </si>
   <si>
-    <t>1,893,036.8</t>
-  </si>
-  <si>
-    <t>1,549,300.0</t>
-  </si>
-  <si>
-    <t>1,044,389.0</t>
+    <t>1,899,142.8</t>
+  </si>
+  <si>
+    <t>1,554,051.0</t>
+  </si>
+  <si>
+    <t>1,135,631.3</t>
   </si>
   <si>
     <t>NRM</t>
@@ -476,10 +476,10 @@
     <t>5,907,022.0</t>
   </si>
   <si>
-    <t>3,128,951.0</t>
-  </si>
-  <si>
-    <t>2,748,462.2</t>
+    <t>3,144,434.0</t>
+  </si>
+  <si>
+    <t>2,753,012.2</t>
   </si>
   <si>
     <t>MFIL</t>
@@ -506,94 +506,94 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>76,780,087.7</t>
+    <t>77,686,776.7</t>
   </si>
   <si>
     <t>50,350,500.0</t>
   </si>
   <si>
-    <t>42,434,064.1</t>
-  </si>
-  <si>
-    <t>41,366,892.29</t>
+    <t>42,769,945.79</t>
+  </si>
+  <si>
+    <t>42,531,105.29</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>610,412,615.4</t>
+    <t>617,987,273.1</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>137,715,163.1</t>
+    <t>140,915,413.8</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>77,258,854.2</t>
+    <t>78,553,987.7</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>67,856,954.3</t>
+    <t>68,416,006.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>56,850,235.2</t>
+    <t>57,278,885.2</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>52,999,204.8</t>
+    <t>53,781,620.8</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>50,101,983.5</t>
+    <t>50,453,957.9</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>43,563,938.1</t>
+    <t>44,912,896.1</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>30,989,365.6</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>30,914,478.7</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>30,697,087.6</t>
+    <t>30,924,978.7</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>23,660,325.6</t>
+    <t>23,924,485.6</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>23,320,671.1</t>
+    <t>23,327,372.1</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>7,732,438.16</t>
+    <t>7,870,472.16</t>
   </si>
   <si>
     <t>Trading</t>
@@ -611,43 +611,43 @@
     <t>Total</t>
   </si>
   <si>
-    <t>1,220,389,477.76</t>
+    <t>1,236,642,242.76</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>91,649,712.2</t>
-  </si>
-  <si>
-    <t>2,972,240.0</t>
-  </si>
-  <si>
-    <t>2,612,959.29</t>
+    <t>91,953,942.2</t>
+  </si>
+  <si>
+    <t>3,015,305.0</t>
+  </si>
+  <si>
+    <t>2,625,895.29</t>
   </si>
   <si>
     <t>1,794,308.2</t>
   </si>
   <si>
-    <t>13,592,686.8</t>
-  </si>
-  <si>
-    <t>7,504,662.0</t>
+    <t>14,216,933.8</t>
+  </si>
+  <si>
+    <t>7,684,369.4</t>
   </si>
   <si>
     <t>6,998,742.2</t>
   </si>
   <si>
-    <t>6,518,685.0</t>
+    <t>6,733,875.0</t>
   </si>
   <si>
     <t>5,721,169.3</t>
   </si>
   <si>
-    <t>3,065,186.0</t>
-  </si>
-  <si>
-    <t>2,005,892.2</t>
+    <t>3,301,686.0</t>
+  </si>
+  <si>
+    <t>2,030,708.8</t>
   </si>
   <si>
     <t>1,701,304.0</t>
@@ -659,7 +659,7 @@
     <t>785,057.8</t>
   </si>
   <si>
-    <t>7,962,014.2</t>
+    <t>8,337,865.2</t>
   </si>
   <si>
     <t>3,219,790.9</t>
@@ -671,13 +671,13 @@
     <t>1,892,758.6</t>
   </si>
   <si>
-    <t>19,197,518.1</t>
-  </si>
-  <si>
-    <t>5,267,194.4</t>
-  </si>
-  <si>
-    <t>4,715,078.4</t>
+    <t>19,447,611.5</t>
+  </si>
+  <si>
+    <t>5,300,218.9</t>
+  </si>
+  <si>
+    <t>4,875,750.09</t>
   </si>
   <si>
     <t>3,545,279.0</t>
@@ -686,7 +686,7 @@
     <t>3,452,732.0</t>
   </si>
   <si>
-    <t>19,991,561.89</t>
+    <t>20,353,946.89</t>
   </si>
   <si>
     <t>11,157,117.0</t>
@@ -701,10 +701,10 @@
     <t>2,626,207.0</t>
   </si>
   <si>
-    <t>10,105,630.4</t>
-  </si>
-  <si>
-    <t>5,586,625.2</t>
+    <t>10,157,425.4</t>
+  </si>
+  <si>
+    <t>5,590,179.2</t>
   </si>
   <si>
     <t>4,557,969.59</t>
@@ -713,10 +713,10 @@
     <t>3,313,849.1</t>
   </si>
   <si>
-    <t>2,437,092.4</t>
-  </si>
-  <si>
-    <t>6,451,171.5</t>
+    <t>2,512,428.4</t>
+  </si>
+  <si>
+    <t>6,583,340.5</t>
   </si>
   <si>
     <t>3,770,900.8</t>
@@ -725,49 +725,49 @@
     <t>1,553,566.4</t>
   </si>
   <si>
-    <t>1,081,478.39</t>
+    <t>1,182,288.39</t>
   </si>
   <si>
     <t>935,622.0</t>
   </si>
   <si>
-    <t>22,526,540.2</t>
-  </si>
-  <si>
-    <t>11,937,523.9</t>
+    <t>22,770,260.2</t>
+  </si>
+  <si>
+    <t>12,105,868.0</t>
   </si>
   <si>
     <t>11,160,706.7</t>
   </si>
   <si>
-    <t>8,971,389.6</t>
-  </si>
-  <si>
-    <t>6,091,710.1</t>
-  </si>
-  <si>
-    <t>86,021,579.4</t>
-  </si>
-  <si>
-    <t>2,758,999.5</t>
-  </si>
-  <si>
-    <t>1,270,867.1</t>
-  </si>
-  <si>
-    <t>1,195,129.2</t>
+    <t>9,009,236.6</t>
+  </si>
+  <si>
+    <t>6,144,065.5</t>
+  </si>
+  <si>
+    <t>86,043,467.4</t>
+  </si>
+  <si>
+    <t>2,763,974.5</t>
+  </si>
+  <si>
+    <t>1,343,029.2</t>
+  </si>
+  <si>
+    <t>1,280,867.1</t>
   </si>
   <si>
     <t>930,967.8</t>
   </si>
   <si>
-    <t>58,800,600.9</t>
+    <t>58,822,133.9</t>
   </si>
   <si>
     <t>4,215,764.0</t>
   </si>
   <si>
-    <t>2,713,577.5</t>
+    <t>2,795,198.5</t>
   </si>
   <si>
     <t>2,152,614.0</t>
@@ -776,13 +776,13 @@
     <t>1,248,597.2</t>
   </si>
   <si>
-    <t>10,270,445.1</t>
-  </si>
-  <si>
-    <t>8,695,364.0</t>
-  </si>
-  <si>
-    <t>4,307,098.2</t>
+    <t>10,494,582.1</t>
+  </si>
+  <si>
+    <t>8,712,314.0</t>
+  </si>
+  <si>
+    <t>4,309,623.2</t>
   </si>
   <si>
     <t>3,105,862.0</t>
@@ -791,10 +791,10 @@
     <t>2,935,214.1</t>
   </si>
   <si>
-    <t>11,117,388.5</t>
-  </si>
-  <si>
-    <t>5,583,479.4</t>
+    <t>11,160,716.5</t>
+  </si>
+  <si>
+    <t>5,708,442.2</t>
   </si>
   <si>
     <t>3,401,123.6</t>
@@ -806,13 +806,13 @@
     <t>2,603,583.4</t>
   </si>
   <si>
-    <t>15,535,529.9</t>
+    <t>15,913,512.5</t>
   </si>
   <si>
     <t>7,373,226.6</t>
   </si>
   <si>
-    <t>4,250,795.09</t>
+    <t>4,255,586.09</t>
   </si>
   <si>
     <t>3,092,500.0</t>
@@ -1627,7 +1627,7 @@
         <v>54</v>
       </c>
       <c r="D9" s="10">
-        <v>0.6212556881544462</v>
+        <v>0.6181565243963609</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>63</v>
@@ -1636,7 +1636,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12">
-        <v>0.04589315407021188</v>
+        <v>0.04531037644215768</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>72</v>
@@ -1645,7 +1645,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.01592252627267097</v>
+        <v>0.01582092251305699</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>81</v>
@@ -1654,7 +1654,7 @@
         <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.02976803193708711</v>
+        <v>0.02955835780453845</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>74</v>
@@ -1663,7 +1663,7 @@
         <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.0755872126959856</v>
+        <v>0.07490037954978661</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>92</v>
@@ -1672,7 +1672,7 @@
         <v>99</v>
       </c>
       <c r="S9" s="16">
-        <v>0.100342690630557</v>
+        <v>0.09920605415564146</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>106</v>
@@ -1681,7 +1681,7 @@
         <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.03204219944250882</v>
+        <v>0.03182398673202905</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1693,7 +1693,7 @@
         <v>56</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02053524497164861</v>
+        <v>0.02043280391848321</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>65</v>
@@ -1702,7 +1702,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04324047028367035</v>
+        <v>0.04269137795784518</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>74</v>
@@ -1711,7 +1711,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.007297566788071494</v>
+        <v>0.007251000043008257</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>83</v>
@@ -1720,7 +1720,7 @@
         <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02474582338354452</v>
+        <v>0.02457152368300963</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>92</v>
@@ -1729,7 +1729,7 @@
         <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.05530052357184797</v>
+        <v>0.0566975628092502</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>74</v>
@@ -1738,7 +1738,7 @@
         <v>100</v>
       </c>
       <c r="S10" s="16">
-        <v>0.05575702208873098</v>
+        <v>0.05881212691091917</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>108</v>
@@ -1747,7 +1747,7 @@
         <v>109</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02653201556923302</v>
+        <v>0.02635132812790298</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1759,7 +1759,7 @@
         <v>58</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02016753966746907</v>
+        <v>0.02006693292982641</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>57</v>
@@ -1768,7 +1768,7 @@
         <v>67</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03830335269392467</v>
+        <v>0.03925713076355368</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1777,7 +1777,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.006370146534059303</v>
+        <v>0.006329497781087027</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>85</v>
@@ -1786,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02392517043692447</v>
+        <v>0.02375665108811285</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>94</v>
@@ -1795,7 +1795,7 @@
         <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02162696502030932</v>
+        <v>0.02148276314384048</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>94</v>
@@ -1804,7 +1804,7 @@
         <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03188809974175685</v>
+        <v>0.03152688581521713</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>110</v>
@@ -1813,7 +1813,7 @@
         <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02629750931429314</v>
+        <v>0.02611841889958441</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1825,7 +1825,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01799566861226907</v>
+        <v>0.01790589635741642</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>68</v>
@@ -1834,7 +1834,7 @@
         <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03622160355604857</v>
+        <v>0.037515823670334</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1843,7 +1843,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.00599728594846956</v>
+        <v>0.005959016468525888</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>87</v>
@@ -1852,7 +1852,7 @@
         <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01862129235747257</v>
+        <v>0.01849013140836313</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>57</v>
@@ -1861,7 +1861,7 @@
         <v>96</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02159964929060824</v>
+        <v>0.02140338123745576</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>102</v>
@@ -1870,7 +1870,7 @@
         <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02875458169880192</v>
+        <v>0.02842886284300473</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>112</v>
@@ -1879,7 +1879,7 @@
         <v>113</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01810718298760445</v>
+        <v>0.01798387005816689</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1891,7 +1891,7 @@
         <v>62</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01610089651335395</v>
+        <v>0.01602057641987504</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>70</v>
@@ -1900,7 +1900,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.0196164154137803</v>
+        <v>0.01936731490462203</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>55</v>
@@ -1909,7 +1909,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0054075744210425</v>
+        <v>0.005373067968852604</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>89</v>
@@ -1918,7 +1918,7 @@
         <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01255758763692514</v>
+        <v>0.01246913700302899</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>97</v>
@@ -1927,7 +1927,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02144749488970063</v>
+        <v>0.02125260940751692</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>104</v>
@@ -1936,7 +1936,7 @@
         <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02572055280760295</v>
+        <v>0.02542920205457452</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>92</v>
@@ -1945,7 +1945,7 @@
         <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01756326372815129</v>
+        <v>0.01744365497938648</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2025,7 +2025,7 @@
         <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.01208431283148863</v>
+        <v>0.01212245552706269</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>97</v>
@@ -2034,7 +2034,7 @@
         <v>123</v>
       </c>
       <c r="G16" s="12">
-        <v>0.0815105148923094</v>
+        <v>0.08047544756052953</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>53</v>
@@ -2043,7 +2043,7 @@
         <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>0.731698766034476</v>
+        <v>0.7270296988110411</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>134</v>
@@ -2052,7 +2052,7 @@
         <v>135</v>
       </c>
       <c r="M16" s="16">
-        <v>0.5257175529080131</v>
+        <v>0.5220146083497516</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>72</v>
@@ -2061,7 +2061,7 @@
         <v>140</v>
       </c>
       <c r="P16" s="18">
-        <v>0.08202982231745991</v>
+        <v>0.08128444755187554</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>92</v>
@@ -2070,7 +2070,7 @@
         <v>146</v>
       </c>
       <c r="S16" s="16">
-        <v>0.02610871134237357</v>
+        <v>0.02581296370556719</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>108</v>
@@ -2079,7 +2079,7 @@
         <v>152</v>
       </c>
       <c r="V16" s="18">
-        <v>0.07888394382061141</v>
+        <v>0.07834673103578636</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2091,7 +2091,7 @@
         <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.009067443396441232</v>
+        <v>0.009022210020733687</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>68</v>
@@ -2100,7 +2100,7 @@
         <v>124</v>
       </c>
       <c r="G17" s="12">
-        <v>0.06024699851943666</v>
+        <v>0.05948194753076794</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>57</v>
@@ -2109,7 +2109,7 @@
         <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>0.03164838657191463</v>
+        <v>0.03148933697279381</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>92</v>
@@ -2118,7 +2118,7 @@
         <v>136</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02197462754012506</v>
+        <v>0.02181984703675509</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>92</v>
@@ -2127,7 +2127,7 @@
         <v>141</v>
       </c>
       <c r="P17" s="18">
-        <v>0.03488603572734947</v>
+        <v>0.0345690391769753</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>74</v>
@@ -2136,7 +2136,7 @@
         <v>147</v>
       </c>
       <c r="S17" s="16">
-        <v>0.0231215549045266</v>
+        <v>0.0229333783220423</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>59</v>
@@ -2145,7 +2145,7 @@
         <v>153</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04178484436005924</v>
+        <v>0.04170563862091285</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2157,7 +2157,7 @@
         <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.007741191601201038</v>
+        <v>0.00770257429610061</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>57</v>
@@ -2166,7 +2166,7 @@
         <v>125</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02817042397561797</v>
+        <v>0.02781269975294469</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>129</v>
@@ -2175,7 +2175,7 @@
         <v>130</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01957067291992609</v>
+        <v>0.01944578985094646</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>83</v>
@@ -2184,7 +2184,7 @@
         <v>137</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01509660986971505</v>
+        <v>0.01499027537687561</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>57</v>
@@ -2193,7 +2193,7 @@
         <v>142</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02609222840025139</v>
+        <v>0.0259086936792778</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>83</v>
@@ -2202,7 +2202,7 @@
         <v>148</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01892315300663096</v>
+        <v>0.01876617151419481</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>57</v>
@@ -2211,7 +2211,7 @@
         <v>154</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03670369566557802</v>
+        <v>0.03651408550224437</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2223,7 +2223,7 @@
         <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.007230148098638587</v>
+        <v>0.007194080158529331</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>74</v>
@@ -2232,16 +2232,16 @@
         <v>126</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02578155036368451</v>
+        <v>0.02545416143012982</v>
       </c>
       <c r="H19" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="J19" s="14">
-        <v>0.01149394764022822</v>
+        <v>0.01242951068622023</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>106</v>
@@ -2250,7 +2250,7 @@
         <v>138</v>
       </c>
       <c r="M19" s="16">
-        <v>0.0150741792541243</v>
+        <v>0.01496800275358602</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>55</v>
@@ -2259,7 +2259,7 @@
         <v>143</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02302994599645043</v>
+        <v>0.02282068136422811</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>89</v>
@@ -2268,7 +2268,7 @@
         <v>149</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01275616913796057</v>
+        <v>0.01371348286040035</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>155</v>
@@ -2277,7 +2277,7 @@
         <v>156</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03125726238795106</v>
+        <v>0.03104439522943749</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2289,7 +2289,7 @@
         <v>122</v>
       </c>
       <c r="D20" s="10">
-        <v>0.006400541223301426</v>
+        <v>0.007181649497120387</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>83</v>
@@ -2298,16 +2298,16 @@
         <v>127</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02014113273065059</v>
+        <v>0.02073741004076333</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>133</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01109741763982776</v>
+        <v>0.01142060323036169</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>68</v>
@@ -2316,7 +2316,7 @@
         <v>139</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01503227878050447</v>
+        <v>0.01492639741017427</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>144</v>
@@ -2325,7 +2325,7 @@
         <v>145</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01780501063829855</v>
+        <v>0.01764322306817085</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>150</v>
@@ -2334,7 +2334,7 @@
         <v>151</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01111610961671137</v>
+        <v>0.01099019137024902</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>74</v>
@@ -2343,7 +2343,7 @@
         <v>157</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02830332809949864</v>
+        <v>0.02811057772506597</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2413,7 +2413,7 @@
         <v>168</v>
       </c>
       <c r="D31" s="22">
-        <v>0.5001785303167312</v>
+        <v>0.4997300364903799</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2424,7 +2424,7 @@
         <v>170</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1128452560511857</v>
+        <v>0.1139500244512899</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2435,7 +2435,7 @@
         <v>172</v>
       </c>
       <c r="D33" s="22">
-        <v>0.06330671937765889</v>
+        <v>0.06352199931702097</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2446,7 +2446,7 @@
         <v>174</v>
       </c>
       <c r="D34" s="22">
-        <v>0.0556027035111365</v>
+        <v>0.05532400854050217</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2457,7 +2457,7 @@
         <v>176</v>
       </c>
       <c r="D35" s="22">
-        <v>0.04658368187863062</v>
+        <v>0.0463180726158619</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2468,7 +2468,7 @@
         <v>178</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04342810698210784</v>
+        <v>0.04349004015904186</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2479,7 +2479,7 @@
         <v>180</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04105409331450577</v>
+        <v>0.04079915448092274</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2490,7 +2490,7 @@
         <v>182</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03569675000800623</v>
+        <v>0.03631842302245891</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2501,7 +2501,7 @@
         <v>184</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02533164966051895</v>
+        <v>0.02505928111499441</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2512,7 +2512,7 @@
         <v>186</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02515351710205162</v>
+        <v>0.02500721520799749</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2523,7 +2523,7 @@
         <v>188</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01938752015744027</v>
+        <v>0.01934632731500756</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2534,7 +2534,7 @@
         <v>190</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01910920368045504</v>
+        <v>0.01886347667368762</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2545,7 +2545,7 @@
         <v>192</v>
       </c>
       <c r="D43" s="22">
-        <v>0.006336041321982498</v>
+        <v>0.006364388897498995</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2556,7 +2556,7 @@
         <v>194</v>
       </c>
       <c r="D44" s="22">
-        <v>0.004839446838594807</v>
+        <v>0.004775843648053516</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2567,7 +2567,7 @@
         <v>196</v>
       </c>
       <c r="D45" s="22">
-        <v>0.001146779798993996</v>
+        <v>0.00113170806528207</v>
       </c>
     </row>
     <row r="46" spans="2:4">
@@ -2963,7 +2963,7 @@
         <v>200</v>
       </c>
       <c r="D9" s="10">
-        <v>0.7428653213373168</v>
+        <v>0.7416131322297763</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>167</v>
@@ -2972,7 +2972,7 @@
         <v>204</v>
       </c>
       <c r="G9" s="12">
-        <v>0.112229833468461</v>
+        <v>0.1158934025704477</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>167</v>
@@ -2981,7 +2981,7 @@
         <v>209</v>
       </c>
       <c r="J9" s="14">
-        <v>0.02926157897314428</v>
+        <v>0.03131818040393517</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>167</v>
@@ -2990,7 +2990,7 @@
         <v>214</v>
       </c>
       <c r="M9" s="16">
-        <v>0.08329891783965875</v>
+        <v>0.08661666540997059</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>167</v>
@@ -2999,7 +2999,7 @@
         <v>218</v>
       </c>
       <c r="P9" s="18">
-        <v>0.22904311655441</v>
+        <v>0.2299186053316553</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>167</v>
@@ -3008,7 +3008,7 @@
         <v>223</v>
       </c>
       <c r="S9" s="16">
-        <v>0.2441769732622694</v>
+        <v>0.2457870806789569</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>167</v>
@@ -3017,7 +3017,7 @@
         <v>228</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1349532777676235</v>
+        <v>0.1347211972174583</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3029,7 +3029,7 @@
         <v>201</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02409144523960247</v>
+        <v>0.02431858528495047</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>169</v>
@@ -3038,7 +3038,7 @@
         <v>205</v>
       </c>
       <c r="G10" s="12">
-        <v>0.06196324383028436</v>
+        <v>0.06264133524868981</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>169</v>
@@ -3047,7 +3047,7 @@
         <v>210</v>
       </c>
       <c r="J10" s="14">
-        <v>0.01914910645615441</v>
+        <v>0.01926231160269593</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>171</v>
@@ -3056,7 +3056,7 @@
         <v>215</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03368558393678586</v>
+        <v>0.03344831613197202</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>169</v>
@@ -3065,7 +3065,7 @@
         <v>219</v>
       </c>
       <c r="P10" s="18">
-        <v>0.06284221817579302</v>
+        <v>0.0626616249219335</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>173</v>
@@ -3074,7 +3074,7 @@
         <v>224</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1362730472496504</v>
+        <v>0.1347294079962232</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>169</v>
@@ -3083,7 +3083,7 @@
         <v>229</v>
       </c>
       <c r="V10" s="18">
-        <v>0.07460527968638207</v>
+        <v>0.07414434316043642</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3095,7 +3095,7 @@
         <v>202</v>
       </c>
       <c r="D11" s="10">
-        <v>0.021179301095894</v>
+        <v>0.02117797662339318</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>175</v>
@@ -3104,7 +3104,7 @@
         <v>206</v>
       </c>
       <c r="G11" s="12">
-        <v>0.05778604945084812</v>
+        <v>0.05705224900684146</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>181</v>
@@ -3113,7 +3113,7 @@
         <v>211</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0162413769844069</v>
+        <v>0.01613773859595871</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>189</v>
@@ -3122,7 +3122,7 @@
         <v>82</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02976803193708711</v>
+        <v>0.02955835780453845</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>173</v>
@@ -3131,7 +3131,7 @@
         <v>220</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05625499327094688</v>
+        <v>0.05764335959393671</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>169</v>
@@ -3140,7 +3140,7 @@
         <v>225</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07475848150377613</v>
+        <v>0.07391165134253058</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>179</v>
@@ -3149,7 +3149,7 @@
         <v>230</v>
       </c>
       <c r="V11" s="18">
-        <v>0.06086833904841638</v>
+        <v>0.06045381553014205</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3161,7 +3161,7 @@
         <v>56</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02053524497164861</v>
+        <v>0.02043280391848321</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>173</v>
@@ -3170,7 +3170,7 @@
         <v>207</v>
       </c>
       <c r="G12" s="12">
-        <v>0.05382239308150283</v>
+        <v>0.05489310826178802</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>177</v>
@@ -3179,7 +3179,7 @@
         <v>212</v>
       </c>
       <c r="J12" s="14">
-        <v>0.009396340500930907</v>
+        <v>0.009336381201435432</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>169</v>
@@ -3188,7 +3188,7 @@
         <v>216</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0230532503515081</v>
+        <v>0.02289087245967785</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>171</v>
@@ -3197,16 +3197,16 @@
         <v>221</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04229826725439587</v>
+        <v>0.04191391848770764</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="R12" s="15" t="s">
         <v>226</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03366270137856098</v>
+        <v>0.03328138556979984</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>171</v>
@@ -3215,7 +3215,7 @@
         <v>231</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04425402279429189</v>
+        <v>0.04395264553456593</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3227,7 +3227,7 @@
         <v>203</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01454373729687699</v>
+        <v>0.01447118516673635</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>187</v>
@@ -3236,7 +3236,7 @@
         <v>208</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04723759821964497</v>
+        <v>0.04663774806763089</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>171</v>
@@ -3245,7 +3245,7 @@
         <v>213</v>
       </c>
       <c r="J13" s="14">
-        <v>0.007494498152210961</v>
+        <v>0.007446674761899363</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>187</v>
@@ -3254,7 +3254,7 @@
         <v>217</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01980211779975317</v>
+        <v>0.01966263958765421</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>181</v>
@@ -3263,7 +3263,7 @@
         <v>222</v>
       </c>
       <c r="P13" s="18">
-        <v>0.04119410091386454</v>
+        <v>0.04081978529980286</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>181</v>
@@ -3272,7 +3272,7 @@
         <v>227</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03207649705549944</v>
+        <v>0.03171314904966375</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>177</v>
@@ -3281,7 +3281,7 @@
         <v>232</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03254558049169937</v>
+        <v>0.03332314525008898</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3361,7 +3361,7 @@
         <v>233</v>
       </c>
       <c r="D16" s="10">
-        <v>0.05228987057691644</v>
+        <v>0.05309496963296199</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>167</v>
@@ -3370,7 +3370,7 @@
         <v>238</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1859933869193979</v>
+        <v>0.1856182893664766</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>167</v>
@@ -3379,7 +3379,7 @@
         <v>243</v>
       </c>
       <c r="J16" s="14">
-        <v>0.8211988567766202</v>
+        <v>0.8161662964356136</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>167</v>
@@ -3388,7 +3388,7 @@
         <v>248</v>
       </c>
       <c r="M16" s="16">
-        <v>0.6151742888491286</v>
+        <v>0.61106493910657</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>167</v>
@@ -3397,7 +3397,7 @@
         <v>253</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1225353580526104</v>
+        <v>0.1240717750851077</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>167</v>
@@ -3406,7 +3406,7 @@
         <v>258</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1357878032786804</v>
+        <v>0.1347728742881051</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>167</v>
@@ -3415,7 +3415,7 @@
         <v>263</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2074656007468787</v>
+        <v>0.2110660301708923</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3427,7 +3427,7 @@
         <v>234</v>
       </c>
       <c r="D17" s="10">
-        <v>0.03056497797189094</v>
+        <v>0.03041250311523641</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>171</v>
@@ -3436,7 +3436,7 @@
         <v>239</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09856375998619886</v>
+        <v>0.09868444583941866</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>169</v>
@@ -3445,7 +3445,7 @@
         <v>244</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02633859144473307</v>
+        <v>0.02621771180629428</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>173</v>
@@ -3454,7 +3454,7 @@
         <v>249</v>
       </c>
       <c r="M17" s="16">
-        <v>0.04410549519836213</v>
+        <v>0.0437948336986066</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>181</v>
@@ -3463,7 +3463,7 @@
         <v>254</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1037432682579432</v>
+        <v>0.103000982104741</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>169</v>
@@ -3472,7 +3472,7 @@
         <v>259</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06819662750633967</v>
+        <v>0.06893313372860192</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>179</v>
@@ -3481,7 +3481,7 @@
         <v>264</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09846403024925887</v>
+        <v>0.09779347381745075</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3493,7 +3493,7 @@
         <v>235</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01259240836933974</v>
+        <v>0.01252959053702145</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>173</v>
@@ -3502,16 +3502,16 @@
         <v>240</v>
       </c>
       <c r="G18" s="12">
-        <v>0.09214986505326798</v>
+        <v>0.0909796931426798</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>245</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01213224189690963</v>
+        <v>0.01273931887325225</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>169</v>
@@ -3520,7 +3520,7 @@
         <v>250</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02838955866519889</v>
+        <v>0.02903750149725996</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>169</v>
@@ -3529,7 +3529,7 @@
         <v>255</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05138743403679298</v>
+        <v>0.05095034707212994</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>177</v>
@@ -3538,7 +3538,7 @@
         <v>260</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04154132981169788</v>
+        <v>0.04107076847450675</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>169</v>
@@ -3547,7 +3547,7 @@
         <v>265</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05676624902723068</v>
+        <v>0.05644320599725734</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3559,7 +3559,7 @@
         <v>236</v>
       </c>
       <c r="D19" s="10">
-        <v>0.008765906404399676</v>
+        <v>0.009535214940713337</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>169</v>
@@ -3568,16 +3568,16 @@
         <v>241</v>
       </c>
       <c r="G19" s="12">
-        <v>0.07407347609809439</v>
+        <v>0.07344136920270469</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>246</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01140921545019152</v>
+        <v>0.01214967956106828</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>177</v>
@@ -3586,16 +3586,16 @@
         <v>251</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02252073561065731</v>
+        <v>0.02236210854006352</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O19" s="17" t="s">
         <v>256</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03705563960728406</v>
+        <v>0.03671892866600023</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>173</v>
@@ -3604,16 +3604,16 @@
         <v>261</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03647110712129614</v>
+        <v>0.03605797896642891</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>266</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04129806800537408</v>
+        <v>0.04101682128967343</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3625,7 +3625,7 @@
         <v>237</v>
       </c>
       <c r="D20" s="10">
-        <v>0.007583669615497854</v>
+        <v>0.007545838116368302</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>179</v>
@@ -3634,7 +3634,7 @@
         <v>242</v>
       </c>
       <c r="G20" s="12">
-        <v>0.05029701780969028</v>
+        <v>0.05008510740977769</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>189</v>
@@ -3643,7 +3643,7 @@
         <v>247</v>
       </c>
       <c r="J20" s="14">
-        <v>0.008887417533929227</v>
+        <v>0.008830705739629583</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>187</v>
@@ -3652,7 +3652,7 @@
         <v>252</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01306287491645367</v>
+        <v>0.01297086524068848</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>173</v>
@@ -3661,7 +3661,7 @@
         <v>257</v>
       </c>
       <c r="P20" s="18">
-        <v>0.03501966148522332</v>
+        <v>0.03470145072683142</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>171</v>
@@ -3670,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="S20" s="16">
-        <v>0.0318001723641157</v>
+        <v>0.03143995443901806</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>171</v>
@@ -3679,7 +3679,7 @@
         <v>267</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03192703225140831</v>
+        <v>0.03170960384866539</v>
       </c>
     </row>
   </sheetData>
